--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6970,0.1456,0.0974,0.0212</t>
-  </si>
-  <si>
-    <t>0.8711,0.0691,0.0289,0.0050</t>
-  </si>
-  <si>
-    <t>0.8181,0.0949,0.0488,0.0069</t>
-  </si>
-  <si>
-    <t>0.6778,0.2292,0.0464,0.0086</t>
-  </si>
-  <si>
-    <t>0.7997,0.0519,0.0145,0.0178</t>
-  </si>
-  <si>
-    <t>0.8289,0.0693,0.0331,0.0091</t>
-  </si>
-  <si>
-    <t>0.8711,0.0422,0.0358,0.0083</t>
-  </si>
-  <si>
-    <t>0.8165,0.0576,0.0280,0.0125</t>
-  </si>
-  <si>
-    <t>0.7485,0.0527,0.0182,0.0283</t>
-  </si>
-  <si>
-    <t>0.5393,0.4481,0.0687,0.0077</t>
-  </si>
-  <si>
-    <t>0.8336,0.0643,0.0307,0.0085</t>
-  </si>
-  <si>
-    <t>0.6363,0.2863,0.0432,0.0088</t>
-  </si>
-  <si>
-    <t>0.9188,0.0406,0.0297,0.0008</t>
-  </si>
-  <si>
-    <t>0.9135,0.0257,0.0488,0.0005</t>
-  </si>
-  <si>
-    <t>0.8513,0.0337,0.1347,0.0006</t>
-  </si>
-  <si>
-    <t>0.9650,0.0101,0.0197,0.0001</t>
-  </si>
-  <si>
-    <t>0.7916,0.1413,0.0648,0.0042</t>
-  </si>
-  <si>
-    <t>0.7521,0.2460,0.0540,0.0024</t>
-  </si>
-  <si>
-    <t>0.7918,0.2250,0.0452,0.0012</t>
-  </si>
-  <si>
-    <t>0.8213,0.0576,0.0370,0.0132</t>
-  </si>
-  <si>
-    <t>0.1769,0.8496,0.0874,0.0039</t>
-  </si>
-  <si>
-    <t>0.4785,0.4654,0.1589,0.0054</t>
-  </si>
-  <si>
-    <t>0.9786,0.0052,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.9682,0.0060,0.0250,0.0001</t>
-  </si>
-  <si>
-    <t>0.8936,0.0101,0.1271,0.0001</t>
-  </si>
-  <si>
-    <t>0.9167,0.0223,0.0527,0.0003</t>
-  </si>
-  <si>
-    <t>0.9592,0.0027,0.0401,0.0000</t>
-  </si>
-  <si>
-    <t>0.9630,0.0045,0.0206,0.0003</t>
-  </si>
-  <si>
-    <t>0.5640,0.0089,0.6353,0.0007</t>
-  </si>
-  <si>
-    <t>0.8675,0.1414,0.0226,0.0007</t>
-  </si>
-  <si>
-    <t>0.7548,0.1526,0.0483,0.0061</t>
-  </si>
-  <si>
-    <t>0.1562,0.0410,0.9196,0.0020</t>
-  </si>
-  <si>
-    <t>0.5854,0.4904,0.0675,0.0006</t>
-  </si>
-  <si>
-    <t>0.8516,0.1123,0.0227,0.0041</t>
-  </si>
-  <si>
-    <t>0.8601,0.0885,0.0599,0.0022</t>
-  </si>
-  <si>
-    <t>0.7889,0.1645,0.0519,0.0030</t>
-  </si>
-  <si>
-    <t>0.9430,0.0265,0.0135,0.0011</t>
-  </si>
-  <si>
-    <t>0.9490,0.0238,0.0128,0.0008</t>
-  </si>
-  <si>
-    <t>0.9738,0.0004,0.0280,0.0000</t>
-  </si>
-  <si>
-    <t>0.9834,0.0007,0.0165,0.0000</t>
-  </si>
-  <si>
-    <t>0.9853,0.0012,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9710,0.0009,0.0376,0.0000</t>
-  </si>
-  <si>
-    <t>0.2999,0.7550,0.0218,0.0004</t>
-  </si>
-  <si>
-    <t>0.9309,0.0075,0.0641,0.0001</t>
-  </si>
-  <si>
-    <t>0.9364,0.0392,0.0170,0.0005</t>
-  </si>
-  <si>
-    <t>0.8076,0.3304,0.0123,0.0003</t>
-  </si>
-  <si>
-    <t>0.3272,0.7884,0.0561,0.0005</t>
-  </si>
-  <si>
-    <t>0.7251,0.3411,0.0632,0.0007</t>
-  </si>
-  <si>
-    <t>0.8555,0.0219,0.1135,0.0004</t>
-  </si>
-  <si>
-    <t>0.9138,0.0036,0.0999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9512,0.0049,0.0395,0.0004</t>
-  </si>
-  <si>
-    <t>0.9731,0.0031,0.0175,0.0001</t>
-  </si>
-  <si>
-    <t>0.6483,0.0189,0.4603,0.0009</t>
-  </si>
-  <si>
-    <t>0.7335,0.0261,0.3468,0.0004</t>
-  </si>
-  <si>
-    <t>0.8650,0.0461,0.0225,0.0100</t>
-  </si>
-  <si>
-    <t>0.6946,0.1945,0.0495,0.0115</t>
-  </si>
-  <si>
-    <t>0.7163,0.1563,0.0471,0.0134</t>
-  </si>
-  <si>
-    <t>0.3715,0.1317,0.6728,0.0122</t>
-  </si>
-  <si>
-    <t>0.8460,0.0529,0.0370,0.0093</t>
-  </si>
-  <si>
-    <t>0.8202,0.1252,0.0408,0.0060</t>
-  </si>
-  <si>
-    <t>0.8442,0.0590,0.0517,0.0082</t>
-  </si>
-  <si>
-    <t>0.8401,0.0197,0.1158,0.0002</t>
-  </si>
-  <si>
-    <t>0.3996,0.0779,0.5158,0.0007</t>
-  </si>
-  <si>
-    <t>0.9054,0.0059,0.1053,0.0001</t>
-  </si>
-  <si>
-    <t>0.6424,0.0656,0.2070,0.0002</t>
-  </si>
-  <si>
-    <t>0.9228,0.0021,0.1220,0.0001</t>
-  </si>
-  <si>
-    <t>0.9037,0.1463,0.0098,0.0003</t>
-  </si>
-  <si>
-    <t>0.0311,0.9773,0.0163,0.0002</t>
-  </si>
-  <si>
-    <t>0.9391,0.0350,0.0219,0.0006</t>
-  </si>
-  <si>
-    <t>0.9241,0.0341,0.0289,0.0014</t>
-  </si>
-  <si>
-    <t>0.6363,0.1860,0.2464,0.0010</t>
-  </si>
-  <si>
-    <t>0.8093,0.0714,0.0581,0.0001</t>
-  </si>
-  <si>
-    <t>0.9764,0.0053,0.0134,0.0000</t>
-  </si>
-  <si>
-    <t>0.7959,0.2482,0.0089,0.0000</t>
-  </si>
-  <si>
-    <t>0.8921,0.0107,0.1240,0.0002</t>
-  </si>
-  <si>
-    <t>0.9321,0.0180,0.0326,0.0007</t>
-  </si>
-  <si>
-    <t>0.9076,0.0295,0.0327,0.0042</t>
-  </si>
-  <si>
-    <t>0.9365,0.0450,0.0085,0.0023</t>
-  </si>
-  <si>
-    <t>0.8836,0.0561,0.0265,0.0041</t>
-  </si>
-  <si>
-    <t>0.8782,0.0807,0.0340,0.0022</t>
-  </si>
-  <si>
-    <t>0.9517,0.0200,0.0099,0.0018</t>
-  </si>
-  <si>
-    <t>0.7390,0.0778,0.0838,0.0001</t>
-  </si>
-  <si>
-    <t>0.8780,0.0117,0.1084,0.0000</t>
-  </si>
-  <si>
-    <t>0.7096,0.1173,0.1167,0.0002</t>
-  </si>
-  <si>
-    <t>0.9421,0.0057,0.0566,0.0002</t>
-  </si>
-  <si>
-    <t>0.7618,0.1385,0.0569,0.0000</t>
-  </si>
-  <si>
-    <t>0.5928,0.4689,0.0242,0.0001</t>
-  </si>
-  <si>
-    <t>0.9010,0.0569,0.0151,0.0043</t>
-  </si>
-  <si>
-    <t>0.8293,0.1217,0.0246,0.0036</t>
-  </si>
-  <si>
-    <t>0.7451,0.0700,0.0346,0.0227</t>
-  </si>
-  <si>
-    <t>0.8968,0.0284,0.0185,0.0069</t>
-  </si>
-  <si>
-    <t>0.8724,0.0317,0.0136,0.0130</t>
-  </si>
-  <si>
-    <t>0.7668,0.0909,0.0425,0.0144</t>
-  </si>
-  <si>
-    <t>0.9280,0.0274,0.0113,0.0039</t>
-  </si>
-  <si>
-    <t>0.7617,0.0783,0.0382,0.0189</t>
-  </si>
-  <si>
-    <t>0.8623,0.0639,0.0274,0.0094</t>
-  </si>
-  <si>
-    <t>0.6708,0.0565,0.0401,0.0675</t>
-  </si>
-  <si>
-    <t>0.7453,0.0722,0.0243,0.0269</t>
-  </si>
-  <si>
-    <t>0.8384,0.0872,0.0240,0.0055</t>
-  </si>
-  <si>
-    <t>0.8736,0.0699,0.0170,0.0037</t>
-  </si>
-  <si>
-    <t>0.8848,0.0457,0.0237,0.0046</t>
-  </si>
-  <si>
-    <t>0.8761,0.0316,0.0105,0.0145</t>
-  </si>
-  <si>
-    <t>0.8616,0.0300,0.0219,0.0117</t>
-  </si>
-  <si>
-    <t>0.3985,0.0213,0.7605,0.0011</t>
-  </si>
-  <si>
-    <t>0.8142,0.0112,0.3003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9944,0.0015,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9743,0.0091,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.2450,0.7928,0.0604,0.0054</t>
-  </si>
-  <si>
-    <t>0.8734,0.0917,0.0163,0.0029</t>
-  </si>
-  <si>
-    <t>0.4121,0.6150,0.1342,0.0038</t>
-  </si>
-  <si>
-    <t>0.5881,0.4183,0.0757,0.0050</t>
-  </si>
-  <si>
-    <t>0.4314,0.6071,0.1067,0.0037</t>
-  </si>
-  <si>
-    <t>0.3404,0.7884,0.0473,0.0016</t>
-  </si>
-  <si>
-    <t>0.8870,0.0824,0.0378,0.0012</t>
-  </si>
-  <si>
-    <t>0.9579,0.0313,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.9133,0.0179,0.0799,0.0004</t>
-  </si>
-  <si>
-    <t>0.9417,0.0219,0.0233,0.0009</t>
-  </si>
-  <si>
-    <t>0.9636,0.0114,0.0197,0.0005</t>
-  </si>
-  <si>
-    <t>0.9200,0.0743,0.0135,0.0007</t>
-  </si>
-  <si>
-    <t>0.8811,0.1192,0.0115,0.0007</t>
-  </si>
-  <si>
-    <t>0.2622,0.8215,0.0453,0.0002</t>
-  </si>
-  <si>
-    <t>0.9101,0.0799,0.0156,0.0007</t>
-  </si>
-  <si>
-    <t>0.2844,0.7985,0.0650,0.0005</t>
-  </si>
-  <si>
-    <t>0.8823,0.1020,0.0249,0.0011</t>
-  </si>
-  <si>
-    <t>0.8731,0.1018,0.0263,0.0019</t>
-  </si>
-  <si>
-    <t>0.7918,0.1852,0.0452,0.0021</t>
-  </si>
-  <si>
-    <t>0.8897,0.0167,0.0153,0.0099</t>
-  </si>
-  <si>
-    <t>0.8412,0.0329,0.0165,0.0209</t>
-  </si>
-  <si>
-    <t>0.8464,0.0582,0.0311,0.0115</t>
-  </si>
-  <si>
-    <t>0.8003,0.0606,0.0229,0.0202</t>
-  </si>
-  <si>
-    <t>0.8241,0.0375,0.0643,0.0224</t>
-  </si>
-  <si>
-    <t>0.8849,0.0316,0.0310,0.0103</t>
-  </si>
-  <si>
-    <t>0.7552,0.0641,0.0355,0.0232</t>
-  </si>
-  <si>
-    <t>0.7797,0.0499,0.0317,0.0283</t>
-  </si>
-  <si>
-    <t>0.8978,0.0842,0.0112,0.0001</t>
-  </si>
-  <si>
-    <t>0.9733,0.0088,0.0115,0.0000</t>
-  </si>
-  <si>
-    <t>0.8628,0.0096,0.1231,0.0001</t>
-  </si>
-  <si>
-    <t>0.9601,0.0023,0.0441,0.0001</t>
-  </si>
-  <si>
-    <t>0.9317,0.0211,0.0435,0.0002</t>
-  </si>
-  <si>
-    <t>0.9108,0.0460,0.0414,0.0004</t>
-  </si>
-  <si>
-    <t>0.9663,0.0085,0.0166,0.0003</t>
-  </si>
-  <si>
-    <t>0.9620,0.0148,0.0132,0.0004</t>
-  </si>
-  <si>
-    <t>0.9680,0.0080,0.0043,0.0018</t>
-  </si>
-  <si>
-    <t>0.9428,0.0144,0.0143,0.0028</t>
-  </si>
-  <si>
-    <t>0.9441,0.0239,0.0054,0.0022</t>
-  </si>
-  <si>
-    <t>0.9334,0.0188,0.0157,0.0017</t>
-  </si>
-  <si>
-    <t>0.7127,0.0802,0.2311,0.0048</t>
-  </si>
-  <si>
-    <t>0.7444,0.2206,0.0564,0.0069</t>
-  </si>
-  <si>
-    <t>0.8322,0.1175,0.0549,0.0032</t>
-  </si>
-  <si>
-    <t>0.8494,0.1019,0.0341,0.0036</t>
-  </si>
-  <si>
-    <t>0.7903,0.1083,0.0265,0.0091</t>
-  </si>
-  <si>
-    <t>0.8655,0.0862,0.0364,0.0021</t>
-  </si>
-  <si>
-    <t>0.8202,0.0877,0.0184,0.0057</t>
-  </si>
-  <si>
-    <t>0.6989,0.1065,0.0409,0.0277</t>
-  </si>
-  <si>
-    <t>0.1974,0.2703,0.7617,0.0163</t>
-  </si>
-  <si>
-    <t>0.7508,0.1531,0.0374,0.0076</t>
-  </si>
-  <si>
-    <t>0.8149,0.0632,0.0429,0.0115</t>
-  </si>
-  <si>
-    <t>0.8342,0.0879,0.0470,0.0046</t>
-  </si>
-  <si>
-    <t>0.8532,0.0577,0.0282,0.0067</t>
-  </si>
-  <si>
-    <t>0.8780,0.0456,0.0199,0.0052</t>
-  </si>
-  <si>
-    <t>0.9488,0.0319,0.0198,0.0003</t>
-  </si>
-  <si>
-    <t>0.8019,0.1639,0.0625,0.0021</t>
-  </si>
-  <si>
-    <t>0.9331,0.0468,0.0166,0.0012</t>
-  </si>
-  <si>
-    <t>0.8601,0.0650,0.0246,0.0068</t>
-  </si>
-  <si>
-    <t>0.7759,0.1161,0.0340,0.0134</t>
-  </si>
-  <si>
-    <t>0.7934,0.0782,0.0569,0.0146</t>
-  </si>
-  <si>
-    <t>0.7392,0.1136,0.0562,0.0225</t>
-  </si>
-  <si>
-    <t>0.7627,0.0845,0.0317,0.0207</t>
-  </si>
-  <si>
-    <t>0.9217,0.0321,0.0213,0.0023</t>
-  </si>
-  <si>
-    <t>0.7887,0.0956,0.0503,0.0079</t>
-  </si>
-  <si>
-    <t>0.8859,0.0645,0.0199,0.0023</t>
-  </si>
-  <si>
-    <t>0.7677,0.1866,0.0394,0.0057</t>
-  </si>
-  <si>
-    <t>0.9031,0.0541,0.0215,0.0022</t>
-  </si>
-  <si>
-    <t>0.8504,0.0807,0.0315,0.0041</t>
-  </si>
-  <si>
-    <t>0.8859,0.0313,0.0376,0.0050</t>
-  </si>
-  <si>
-    <t>0.9302,0.0158,0.0175,0.0053</t>
-  </si>
-  <si>
-    <t>0.8131,0.0750,0.0566,0.0079</t>
-  </si>
-  <si>
-    <t>0.8811,0.0388,0.0175,0.0089</t>
-  </si>
-  <si>
-    <t>0.9003,0.0227,0.0099,0.0102</t>
-  </si>
-  <si>
-    <t>0.4969,0.0933,0.5269,0.0007</t>
-  </si>
-  <si>
-    <t>0.7881,0.0841,0.0671,0.0119</t>
-  </si>
-  <si>
-    <t>0.7256,0.0213,0.3302,0.0034</t>
-  </si>
-  <si>
-    <t>0.9631,0.0053,0.0327,0.0002</t>
-  </si>
-  <si>
-    <t>0.8254,0.0111,0.2396,0.0002</t>
-  </si>
-  <si>
-    <t>0.7907,0.0344,0.1635,0.0013</t>
-  </si>
-  <si>
-    <t>0.8034,0.0253,0.2304,0.0011</t>
-  </si>
-  <si>
-    <t>0.9012,0.0041,0.1212,0.0001</t>
-  </si>
-  <si>
-    <t>0.8288,0.0016,0.3694,0.0001</t>
-  </si>
-  <si>
-    <t>0.9399,0.0454,0.0179,0.0002</t>
-  </si>
-  <si>
-    <t>0.8934,0.0660,0.0414,0.0005</t>
-  </si>
-  <si>
-    <t>0.8153,0.0863,0.1057,0.0017</t>
-  </si>
-  <si>
-    <t>0.8933,0.0452,0.0575,0.0017</t>
-  </si>
-  <si>
-    <t>0.9436,0.0127,0.0443,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0166,0.0131,0.0003</t>
-  </si>
-  <si>
-    <t>0.9480,0.0223,0.0166,0.0006</t>
-  </si>
-  <si>
-    <t>0.8883,0.0660,0.0586,0.0013</t>
-  </si>
-  <si>
-    <t>0.7140,0.1365,0.0573,0.0174</t>
-  </si>
-  <si>
-    <t>0.8115,0.1002,0.0303,0.0062</t>
-  </si>
-  <si>
-    <t>0.5753,0.3850,0.0809,0.0117</t>
-  </si>
-  <si>
-    <t>0.8218,0.0483,0.0270,0.0164</t>
-  </si>
-  <si>
-    <t>0.8941,0.0449,0.0165,0.0041</t>
-  </si>
-  <si>
-    <t>0.9823,0.0067,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9259,0.0337,0.0418,0.0007</t>
-  </si>
-  <si>
-    <t>0.9280,0.0131,0.0418,0.0011</t>
-  </si>
-  <si>
-    <t>0.9334,0.0305,0.0345,0.0005</t>
-  </si>
-  <si>
-    <t>0.9296,0.0315,0.0269,0.0004</t>
-  </si>
-  <si>
-    <t>0.9432,0.0084,0.0344,0.0005</t>
-  </si>
-  <si>
-    <t>0.9693,0.0039,0.0244,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0007,0.0134,0.0000</t>
-  </si>
-  <si>
-    <t>0.9286,0.0081,0.0568,0.0001</t>
-  </si>
-  <si>
-    <t>0.8843,0.0052,0.1410,0.0001</t>
-  </si>
-  <si>
-    <t>0.8123,0.0621,0.0220,0.0146</t>
-  </si>
-  <si>
-    <t>0.8630,0.0754,0.0338,0.0058</t>
-  </si>
-  <si>
-    <t>0.8622,0.0341,0.0322,0.0129</t>
-  </si>
-  <si>
-    <t>0.7460,0.0668,0.0728,0.0230</t>
-  </si>
-  <si>
-    <t>0.7883,0.1043,0.0283,0.0142</t>
-  </si>
-  <si>
-    <t>0.8153,0.0392,0.0216,0.0211</t>
-  </si>
-  <si>
-    <t>0.8232,0.0546,0.0198,0.0180</t>
-  </si>
-  <si>
-    <t>0.8976,0.0688,0.0238,0.0014</t>
-  </si>
-  <si>
-    <t>0.8447,0.0588,0.1159,0.0010</t>
-  </si>
-  <si>
-    <t>0.8832,0.0492,0.0353,0.0033</t>
-  </si>
-  <si>
-    <t>0.8211,0.1361,0.0553,0.0013</t>
-  </si>
-  <si>
-    <t>0.9795,0.0004,0.0186,0.0001</t>
-  </si>
-  <si>
-    <t>0.5919,0.0183,0.5005,0.0025</t>
-  </si>
-  <si>
-    <t>0.9580,0.0027,0.0420,0.0001</t>
-  </si>
-  <si>
-    <t>0.5361,0.0025,0.7609,0.0003</t>
-  </si>
-  <si>
-    <t>0.9430,0.0041,0.0607,0.0002</t>
-  </si>
-  <si>
-    <t>0.7225,0.0075,0.4183,0.0002</t>
-  </si>
-  <si>
-    <t>0.9462,0.0039,0.0462,0.0001</t>
-  </si>
-  <si>
-    <t>0.8791,0.0219,0.1328,0.0004</t>
-  </si>
-  <si>
-    <t>0.9439,0.0167,0.0336,0.0004</t>
-  </si>
-  <si>
-    <t>0.9142,0.0523,0.0296,0.0010</t>
-  </si>
-  <si>
-    <t>0.9661,0.0148,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.7404,0.1295,0.0516,0.0172</t>
-  </si>
-  <si>
-    <t>0.7776,0.0781,0.0379,0.0165</t>
-  </si>
-  <si>
-    <t>0.8165,0.0684,0.0506,0.0128</t>
-  </si>
-  <si>
-    <t>0.9264,0.0210,0.0176,0.0040</t>
-  </si>
-  <si>
-    <t>0.7241,0.0731,0.0159,0.0210</t>
-  </si>
-  <si>
-    <t>0.8994,0.0233,0.0217,0.0085</t>
-  </si>
-  <si>
-    <t>0.8575,0.0178,0.0191,0.0246</t>
-  </si>
-  <si>
-    <t>0.7321,0.0924,0.0733,0.0249</t>
-  </si>
-  <si>
-    <t>0.8078,0.0386,0.1444,0.0002</t>
-  </si>
-  <si>
-    <t>0.9068,0.0128,0.0775,0.0000</t>
-  </si>
-  <si>
-    <t>0.8249,0.0097,0.2096,0.0005</t>
-  </si>
-  <si>
-    <t>0.9681,0.0050,0.0245,0.0002</t>
-  </si>
-  <si>
-    <t>0.7528,0.0038,0.4305,0.0001</t>
-  </si>
-  <si>
-    <t>0.9701,0.0130,0.0110,0.0001</t>
-  </si>
-  <si>
-    <t>0.9267,0.0045,0.1214,0.0001</t>
-  </si>
-  <si>
-    <t>0.9804,0.0016,0.0140,0.0001</t>
-  </si>
-  <si>
-    <t>0.6891,0.1207,0.0521,0.0268</t>
-  </si>
-  <si>
-    <t>0.9255,0.0234,0.0234,0.0023</t>
-  </si>
-  <si>
-    <t>0.9388,0.0223,0.0180,0.0022</t>
-  </si>
-  <si>
-    <t>0.9755,0.0046,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.8892,0.0332,0.0252,0.0064</t>
-  </si>
-  <si>
-    <t>0.8152,0.1326,0.0482,0.0026</t>
+    <t>0.7359,0.2701,0.0510,0.0039</t>
+  </si>
+  <si>
+    <t>0.9181,0.0193,0.0191,0.0040</t>
+  </si>
+  <si>
+    <t>0.8686,0.0444,0.0411,0.0071</t>
+  </si>
+  <si>
+    <t>0.7788,0.1743,0.0821,0.0071</t>
+  </si>
+  <si>
+    <t>0.7991,0.0878,0.0312,0.0136</t>
+  </si>
+  <si>
+    <t>0.9214,0.0193,0.0090,0.0058</t>
+  </si>
+  <si>
+    <t>0.8388,0.0884,0.0380,0.0046</t>
+  </si>
+  <si>
+    <t>0.9082,0.0381,0.0124,0.0051</t>
+  </si>
+  <si>
+    <t>0.9121,0.0229,0.0136,0.0086</t>
+  </si>
+  <si>
+    <t>0.8552,0.0707,0.0133,0.0053</t>
+  </si>
+  <si>
+    <t>0.6924,0.1382,0.0743,0.0205</t>
+  </si>
+  <si>
+    <t>0.8051,0.0535,0.0427,0.0233</t>
+  </si>
+  <si>
+    <t>0.9821,0.0089,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.9117,0.0124,0.0751,0.0007</t>
+  </si>
+  <si>
+    <t>0.9049,0.0684,0.0365,0.0008</t>
+  </si>
+  <si>
+    <t>0.9359,0.0119,0.0549,0.0002</t>
+  </si>
+  <si>
+    <t>0.9116,0.0514,0.0358,0.0005</t>
+  </si>
+  <si>
+    <t>0.5004,0.6546,0.0414,0.0008</t>
+  </si>
+  <si>
+    <t>0.7706,0.2275,0.0480,0.0015</t>
+  </si>
+  <si>
+    <t>0.7399,0.1543,0.0464,0.0097</t>
+  </si>
+  <si>
+    <t>0.5957,0.3830,0.0665,0.0070</t>
+  </si>
+  <si>
+    <t>0.5273,0.5677,0.0836,0.0010</t>
+  </si>
+  <si>
+    <t>0.9827,0.0046,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9757,0.0056,0.0121,0.0001</t>
+  </si>
+  <si>
+    <t>0.9701,0.0039,0.0234,0.0002</t>
+  </si>
+  <si>
+    <t>0.9721,0.0047,0.0176,0.0002</t>
+  </si>
+  <si>
+    <t>0.9846,0.0016,0.0117,0.0001</t>
+  </si>
+  <si>
+    <t>0.9053,0.0256,0.0906,0.0005</t>
+  </si>
+  <si>
+    <t>0.4510,0.0138,0.7401,0.0004</t>
+  </si>
+  <si>
+    <t>0.5974,0.4716,0.0730,0.0017</t>
+  </si>
+  <si>
+    <t>0.8452,0.1056,0.0519,0.0018</t>
+  </si>
+  <si>
+    <t>0.3845,0.0512,0.7384,0.0090</t>
+  </si>
+  <si>
+    <t>0.7288,0.1469,0.1321,0.0013</t>
+  </si>
+  <si>
+    <t>0.8678,0.1040,0.0263,0.0019</t>
+  </si>
+  <si>
+    <t>0.6843,0.1859,0.2123,0.0075</t>
+  </si>
+  <si>
+    <t>0.7970,0.0974,0.0516,0.0061</t>
+  </si>
+  <si>
+    <t>0.9429,0.0256,0.0213,0.0005</t>
+  </si>
+  <si>
+    <t>0.6175,0.1548,0.1191,0.0006</t>
+  </si>
+  <si>
+    <t>0.9648,0.0050,0.0177,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0007,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.9538,0.0085,0.0238,0.0003</t>
+  </si>
+  <si>
+    <t>0.9611,0.0051,0.0346,0.0001</t>
+  </si>
+  <si>
+    <t>0.4190,0.5736,0.0615,0.0007</t>
+  </si>
+  <si>
+    <t>0.8552,0.0121,0.2016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9377,0.0387,0.0076,0.0016</t>
+  </si>
+  <si>
+    <t>0.6479,0.5899,0.0100,0.0003</t>
+  </si>
+  <si>
+    <t>0.0702,0.9587,0.0192,0.0006</t>
+  </si>
+  <si>
+    <t>0.3043,0.8079,0.0388,0.0003</t>
+  </si>
+  <si>
+    <t>0.8358,0.0134,0.1903,0.0010</t>
+  </si>
+  <si>
+    <t>0.7444,0.0097,0.4076,0.0004</t>
+  </si>
+  <si>
+    <t>0.9709,0.0074,0.0167,0.0001</t>
+  </si>
+  <si>
+    <t>0.7153,0.0066,0.4549,0.0002</t>
+  </si>
+  <si>
+    <t>0.8611,0.0096,0.1990,0.0002</t>
+  </si>
+  <si>
+    <t>0.8705,0.0135,0.1397,0.0003</t>
+  </si>
+  <si>
+    <t>0.9015,0.0346,0.0288,0.0045</t>
+  </si>
+  <si>
+    <t>0.8906,0.0266,0.0125,0.0077</t>
+  </si>
+  <si>
+    <t>0.7940,0.1202,0.0790,0.0079</t>
+  </si>
+  <si>
+    <t>0.2287,0.2685,0.7732,0.0094</t>
+  </si>
+  <si>
+    <t>0.8272,0.0513,0.0253,0.0186</t>
+  </si>
+  <si>
+    <t>0.8399,0.0323,0.0262,0.0193</t>
+  </si>
+  <si>
+    <t>0.6989,0.1719,0.0778,0.0084</t>
+  </si>
+  <si>
+    <t>0.6554,0.0900,0.1640,0.0003</t>
+  </si>
+  <si>
+    <t>0.7855,0.0128,0.2465,0.0001</t>
+  </si>
+  <si>
+    <t>0.8815,0.0242,0.0754,0.0008</t>
+  </si>
+  <si>
+    <t>0.1420,0.4519,0.6041,0.0002</t>
+  </si>
+  <si>
+    <t>0.3145,0.0029,0.9015,0.0001</t>
+  </si>
+  <si>
+    <t>0.6498,0.5215,0.0275,0.0006</t>
+  </si>
+  <si>
+    <t>0.0236,0.9799,0.0401,0.0004</t>
+  </si>
+  <si>
+    <t>0.7593,0.1137,0.1508,0.0007</t>
+  </si>
+  <si>
+    <t>0.9641,0.0098,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.6116,0.1625,0.3556,0.0083</t>
+  </si>
+  <si>
+    <t>0.6155,0.2315,0.0911,0.0001</t>
+  </si>
+  <si>
+    <t>0.7677,0.1305,0.0587,0.0001</t>
+  </si>
+  <si>
+    <t>0.0500,0.9524,0.0345,0.0001</t>
+  </si>
+  <si>
+    <t>0.5377,0.3836,0.0410,0.0001</t>
+  </si>
+  <si>
+    <t>0.8597,0.0546,0.0492,0.0051</t>
+  </si>
+  <si>
+    <t>0.9056,0.0334,0.0275,0.0042</t>
+  </si>
+  <si>
+    <t>0.9639,0.0101,0.0059,0.0011</t>
+  </si>
+  <si>
+    <t>0.9421,0.0198,0.0213,0.0015</t>
+  </si>
+  <si>
+    <t>0.9513,0.0124,0.0200,0.0006</t>
+  </si>
+  <si>
+    <t>0.9718,0.0084,0.0037,0.0011</t>
+  </si>
+  <si>
+    <t>0.9019,0.0247,0.0487,0.0001</t>
+  </si>
+  <si>
+    <t>0.7734,0.0354,0.1857,0.0001</t>
+  </si>
+  <si>
+    <t>0.6992,0.0134,0.4306,0.0001</t>
+  </si>
+  <si>
+    <t>0.8590,0.0188,0.1408,0.0003</t>
+  </si>
+  <si>
+    <t>0.3629,0.2758,0.3207,0.0002</t>
+  </si>
+  <si>
+    <t>0.8615,0.1008,0.0308,0.0002</t>
+  </si>
+  <si>
+    <t>0.7116,0.1264,0.0426,0.0187</t>
+  </si>
+  <si>
+    <t>0.8455,0.0567,0.0400,0.0076</t>
+  </si>
+  <si>
+    <t>0.8767,0.0543,0.0276,0.0038</t>
+  </si>
+  <si>
+    <t>0.8953,0.0386,0.0197,0.0053</t>
+  </si>
+  <si>
+    <t>0.7191,0.1631,0.0563,0.0145</t>
+  </si>
+  <si>
+    <t>0.8094,0.0912,0.0208,0.0058</t>
+  </si>
+  <si>
+    <t>0.4908,0.3355,0.1088,0.0296</t>
+  </si>
+  <si>
+    <t>0.7982,0.0819,0.0415,0.0103</t>
+  </si>
+  <si>
+    <t>0.8603,0.0560,0.0189,0.0078</t>
+  </si>
+  <si>
+    <t>0.8443,0.0373,0.0229,0.0168</t>
+  </si>
+  <si>
+    <t>0.8458,0.0637,0.0315,0.0099</t>
+  </si>
+  <si>
+    <t>0.7499,0.0788,0.0445,0.0313</t>
+  </si>
+  <si>
+    <t>0.8642,0.0299,0.0177,0.0144</t>
+  </si>
+  <si>
+    <t>0.8826,0.0444,0.0226,0.0061</t>
+  </si>
+  <si>
+    <t>0.8832,0.0449,0.0192,0.0087</t>
+  </si>
+  <si>
+    <t>0.8518,0.0473,0.0323,0.0097</t>
+  </si>
+  <si>
+    <t>0.3794,0.0098,0.8107,0.0014</t>
+  </si>
+  <si>
+    <t>0.9048,0.0154,0.1084,0.0002</t>
+  </si>
+  <si>
+    <t>0.9848,0.0041,0.0057,0.0001</t>
+  </si>
+  <si>
+    <t>0.9219,0.0257,0.0404,0.0008</t>
+  </si>
+  <si>
+    <t>0.4819,0.5772,0.0640,0.0030</t>
+  </si>
+  <si>
+    <t>0.6412,0.3854,0.0803,0.0033</t>
+  </si>
+  <si>
+    <t>0.4686,0.5514,0.1072,0.0072</t>
+  </si>
+  <si>
+    <t>0.5592,0.3304,0.1555,0.0078</t>
+  </si>
+  <si>
+    <t>0.2792,0.7625,0.1130,0.0017</t>
+  </si>
+  <si>
+    <t>0.0820,0.9282,0.0541,0.0036</t>
+  </si>
+  <si>
+    <t>0.7782,0.1769,0.0579,0.0028</t>
+  </si>
+  <si>
+    <t>0.9423,0.0236,0.0125,0.0011</t>
+  </si>
+  <si>
+    <t>0.9290,0.0205,0.0459,0.0005</t>
+  </si>
+  <si>
+    <t>0.9606,0.0108,0.0188,0.0002</t>
+  </si>
+  <si>
+    <t>0.9251,0.0463,0.0306,0.0003</t>
+  </si>
+  <si>
+    <t>0.8850,0.0608,0.0432,0.0011</t>
+  </si>
+  <si>
+    <t>0.2251,0.8876,0.0275,0.0005</t>
+  </si>
+  <si>
+    <t>0.5927,0.5472,0.0480,0.0010</t>
+  </si>
+  <si>
+    <t>0.9521,0.0387,0.0127,0.0002</t>
+  </si>
+  <si>
+    <t>0.1992,0.7973,0.1987,0.0017</t>
+  </si>
+  <si>
+    <t>0.6791,0.3112,0.0938,0.0016</t>
+  </si>
+  <si>
+    <t>0.8767,0.0432,0.0353,0.0056</t>
+  </si>
+  <si>
+    <t>0.7229,0.1483,0.0626,0.0141</t>
+  </si>
+  <si>
+    <t>0.9102,0.0212,0.0195,0.0069</t>
+  </si>
+  <si>
+    <t>0.8784,0.0327,0.0288,0.0083</t>
+  </si>
+  <si>
+    <t>0.8109,0.0577,0.0779,0.0113</t>
+  </si>
+  <si>
+    <t>0.8618,0.0582,0.0461,0.0050</t>
+  </si>
+  <si>
+    <t>0.8615,0.0845,0.0459,0.0049</t>
+  </si>
+  <si>
+    <t>0.8699,0.0684,0.0295,0.0053</t>
+  </si>
+  <si>
+    <t>0.8318,0.0635,0.0365,0.0111</t>
+  </si>
+  <si>
+    <t>0.7617,0.0528,0.0384,0.0237</t>
+  </si>
+  <si>
+    <t>0.8163,0.1477,0.0310,0.0001</t>
+  </si>
+  <si>
+    <t>0.9542,0.0053,0.0368,0.0000</t>
+  </si>
+  <si>
+    <t>0.8596,0.0201,0.1282,0.0001</t>
+  </si>
+  <si>
+    <t>0.9587,0.0042,0.0367,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0056,0.0051,0.0001</t>
+  </si>
+  <si>
+    <t>0.9431,0.0242,0.0210,0.0006</t>
+  </si>
+  <si>
+    <t>0.9683,0.0100,0.0149,0.0003</t>
+  </si>
+  <si>
+    <t>0.9707,0.0118,0.0060,0.0006</t>
+  </si>
+  <si>
+    <t>0.9759,0.0084,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9594,0.0065,0.0103,0.0017</t>
+  </si>
+  <si>
+    <t>0.8748,0.0456,0.0470,0.0044</t>
+  </si>
+  <si>
+    <t>0.8702,0.0251,0.0144,0.0134</t>
+  </si>
+  <si>
+    <t>0.2644,0.2411,0.5915,0.0021</t>
+  </si>
+  <si>
+    <t>0.9140,0.0230,0.0144,0.0049</t>
+  </si>
+  <si>
+    <t>0.7553,0.2185,0.0571,0.0023</t>
+  </si>
+  <si>
+    <t>0.8090,0.1136,0.0672,0.0073</t>
+  </si>
+  <si>
+    <t>0.8370,0.0508,0.0553,0.0088</t>
+  </si>
+  <si>
+    <t>0.9253,0.0224,0.0239,0.0027</t>
+  </si>
+  <si>
+    <t>0.9158,0.0484,0.0201,0.0016</t>
+  </si>
+  <si>
+    <t>0.7908,0.0793,0.0370,0.0158</t>
+  </si>
+  <si>
+    <t>0.1069,0.3364,0.8574,0.0162</t>
+  </si>
+  <si>
+    <t>0.7212,0.1195,0.0333,0.0209</t>
+  </si>
+  <si>
+    <t>0.5701,0.1330,0.0437,0.0559</t>
+  </si>
+  <si>
+    <t>0.6743,0.3123,0.0768,0.0041</t>
+  </si>
+  <si>
+    <t>0.9198,0.0474,0.0141,0.0012</t>
+  </si>
+  <si>
+    <t>0.9227,0.0277,0.0119,0.0036</t>
+  </si>
+  <si>
+    <t>0.8262,0.0533,0.0491,0.0130</t>
+  </si>
+  <si>
+    <t>0.9125,0.0742,0.0216,0.0007</t>
+  </si>
+  <si>
+    <t>0.9050,0.0782,0.0292,0.0003</t>
+  </si>
+  <si>
+    <t>0.6885,0.2192,0.0778,0.0103</t>
+  </si>
+  <si>
+    <t>0.8577,0.0693,0.0202,0.0059</t>
+  </si>
+  <si>
+    <t>0.8275,0.0652,0.0299,0.0116</t>
+  </si>
+  <si>
+    <t>0.8553,0.0307,0.0161,0.0197</t>
+  </si>
+  <si>
+    <t>0.8636,0.0692,0.0460,0.0046</t>
+  </si>
+  <si>
+    <t>0.8764,0.0217,0.0185,0.0154</t>
+  </si>
+  <si>
+    <t>0.8550,0.0648,0.0221,0.0070</t>
+  </si>
+  <si>
+    <t>0.7239,0.2083,0.0572,0.0082</t>
+  </si>
+  <si>
+    <t>0.8081,0.1444,0.0526,0.0026</t>
+  </si>
+  <si>
+    <t>0.7848,0.1702,0.0435,0.0042</t>
+  </si>
+  <si>
+    <t>0.8127,0.1797,0.0428,0.0029</t>
+  </si>
+  <si>
+    <t>0.8430,0.0686,0.0341,0.0061</t>
+  </si>
+  <si>
+    <t>0.8631,0.0512,0.0263,0.0063</t>
+  </si>
+  <si>
+    <t>0.7898,0.0977,0.0409,0.0081</t>
+  </si>
+  <si>
+    <t>0.8583,0.0597,0.0491,0.0047</t>
+  </si>
+  <si>
+    <t>0.9055,0.0372,0.0277,0.0032</t>
+  </si>
+  <si>
+    <t>0.0745,0.2344,0.9136,0.0010</t>
+  </si>
+  <si>
+    <t>0.6886,0.1403,0.0952,0.0123</t>
+  </si>
+  <si>
+    <t>0.8629,0.0075,0.1359,0.0002</t>
+  </si>
+  <si>
+    <t>0.9594,0.0144,0.0255,0.0001</t>
+  </si>
+  <si>
+    <t>0.9363,0.0062,0.0676,0.0001</t>
+  </si>
+  <si>
+    <t>0.6109,0.0242,0.4121,0.0004</t>
+  </si>
+  <si>
+    <t>0.9838,0.0011,0.0135,0.0000</t>
+  </si>
+  <si>
+    <t>0.9448,0.0031,0.0615,0.0001</t>
+  </si>
+  <si>
+    <t>0.8822,0.0064,0.1704,0.0003</t>
+  </si>
+  <si>
+    <t>0.8722,0.0173,0.1481,0.0008</t>
+  </si>
+  <si>
+    <t>0.8478,0.0676,0.0937,0.0024</t>
+  </si>
+  <si>
+    <t>0.9411,0.0224,0.0331,0.0002</t>
+  </si>
+  <si>
+    <t>0.9069,0.0181,0.0977,0.0002</t>
+  </si>
+  <si>
+    <t>0.9112,0.0604,0.0374,0.0007</t>
+  </si>
+  <si>
+    <t>0.9358,0.0553,0.0177,0.0002</t>
+  </si>
+  <si>
+    <t>0.8980,0.0365,0.0610,0.0014</t>
+  </si>
+  <si>
+    <t>0.9282,0.0317,0.0340,0.0004</t>
+  </si>
+  <si>
+    <t>0.7263,0.2728,0.0556,0.0036</t>
+  </si>
+  <si>
+    <t>0.7432,0.2086,0.0655,0.0043</t>
+  </si>
+  <si>
+    <t>0.5827,0.4260,0.0988,0.0062</t>
+  </si>
+  <si>
+    <t>0.9000,0.0265,0.0172,0.0093</t>
+  </si>
+  <si>
+    <t>0.7940,0.0694,0.0474,0.0120</t>
+  </si>
+  <si>
+    <t>0.9250,0.0281,0.0366,0.0008</t>
+  </si>
+  <si>
+    <t>0.9222,0.0471,0.0266,0.0006</t>
+  </si>
+  <si>
+    <t>0.8965,0.0372,0.0596,0.0011</t>
+  </si>
+  <si>
+    <t>0.9603,0.0053,0.0277,0.0002</t>
+  </si>
+  <si>
+    <t>0.9390,0.0220,0.0144,0.0015</t>
+  </si>
+  <si>
+    <t>0.7682,0.0537,0.2336,0.0023</t>
+  </si>
+  <si>
+    <t>0.9108,0.0065,0.1128,0.0001</t>
+  </si>
+  <si>
+    <t>0.9813,0.0012,0.0121,0.0001</t>
+  </si>
+  <si>
+    <t>0.9716,0.0014,0.0229,0.0000</t>
+  </si>
+  <si>
+    <t>0.9503,0.0108,0.0192,0.0003</t>
+  </si>
+  <si>
+    <t>0.9017,0.0226,0.0091,0.0101</t>
+  </si>
+  <si>
+    <t>0.7439,0.1738,0.0595,0.0082</t>
+  </si>
+  <si>
+    <t>0.8274,0.0867,0.0293,0.0066</t>
+  </si>
+  <si>
+    <t>0.8856,0.0234,0.0212,0.0117</t>
+  </si>
+  <si>
+    <t>0.8494,0.0503,0.0205,0.0074</t>
+  </si>
+  <si>
+    <t>0.7995,0.0861,0.0446,0.0100</t>
+  </si>
+  <si>
+    <t>0.8464,0.0516,0.0167,0.0106</t>
+  </si>
+  <si>
+    <t>0.8836,0.0213,0.0135,0.0134</t>
+  </si>
+  <si>
+    <t>0.9166,0.0251,0.0385,0.0014</t>
+  </si>
+  <si>
+    <t>0.8394,0.1449,0.0513,0.0006</t>
+  </si>
+  <si>
+    <t>0.8332,0.0780,0.0827,0.0043</t>
+  </si>
+  <si>
+    <t>0.7218,0.0224,0.2567,0.0004</t>
+  </si>
+  <si>
+    <t>0.7948,0.0510,0.1163,0.0024</t>
+  </si>
+  <si>
+    <t>0.8703,0.0171,0.1244,0.0004</t>
+  </si>
+  <si>
+    <t>0.2241,0.0215,0.8943,0.0005</t>
+  </si>
+  <si>
+    <t>0.9706,0.0083,0.0114,0.0001</t>
+  </si>
+  <si>
+    <t>0.5520,0.0054,0.6996,0.0004</t>
+  </si>
+  <si>
+    <t>0.9578,0.0039,0.0468,0.0001</t>
+  </si>
+  <si>
+    <t>0.9341,0.0205,0.0390,0.0004</t>
+  </si>
+  <si>
+    <t>0.9389,0.0101,0.0425,0.0005</t>
+  </si>
+  <si>
+    <t>0.9669,0.0065,0.0150,0.0004</t>
+  </si>
+  <si>
+    <t>0.9773,0.0071,0.0072,0.0001</t>
+  </si>
+  <si>
+    <t>0.7904,0.1101,0.0473,0.0081</t>
+  </si>
+  <si>
+    <t>0.6283,0.3324,0.0321,0.0052</t>
+  </si>
+  <si>
+    <t>0.8396,0.0757,0.0386,0.0082</t>
+  </si>
+  <si>
+    <t>0.9027,0.0188,0.0259,0.0089</t>
+  </si>
+  <si>
+    <t>0.6982,0.0756,0.0638,0.0342</t>
+  </si>
+  <si>
+    <t>0.7491,0.1142,0.0418,0.0130</t>
+  </si>
+  <si>
+    <t>0.8159,0.0545,0.0411,0.0153</t>
+  </si>
+  <si>
+    <t>0.7716,0.0729,0.0265,0.0228</t>
+  </si>
+  <si>
+    <t>0.9716,0.0140,0.0097,0.0001</t>
+  </si>
+  <si>
+    <t>0.9283,0.0101,0.0692,0.0001</t>
+  </si>
+  <si>
+    <t>0.9315,0.0027,0.0629,0.0001</t>
+  </si>
+  <si>
+    <t>0.9505,0.0102,0.0304,0.0002</t>
+  </si>
+  <si>
+    <t>0.9641,0.0033,0.0259,0.0003</t>
+  </si>
+  <si>
+    <t>0.9654,0.0089,0.0126,0.0004</t>
+  </si>
+  <si>
+    <t>0.9722,0.0064,0.0142,0.0000</t>
+  </si>
+  <si>
+    <t>0.9690,0.0024,0.0208,0.0004</t>
+  </si>
+  <si>
+    <t>0.8631,0.0711,0.0247,0.0045</t>
+  </si>
+  <si>
+    <t>0.9522,0.0108,0.0253,0.0010</t>
+  </si>
+  <si>
+    <t>0.9584,0.0138,0.0099,0.0013</t>
+  </si>
+  <si>
+    <t>0.9192,0.0107,0.0216,0.0041</t>
+  </si>
+  <si>
+    <t>0.9305,0.0122,0.0093,0.0076</t>
+  </si>
+  <si>
+    <t>0.9163,0.0317,0.0297,0.0020</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
         <v>329</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="517">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,763 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7359,0.2701,0.0510,0.0039</t>
-  </si>
-  <si>
-    <t>0.9181,0.0193,0.0191,0.0040</t>
-  </si>
-  <si>
-    <t>0.8686,0.0444,0.0411,0.0071</t>
-  </si>
-  <si>
-    <t>0.7788,0.1743,0.0821,0.0071</t>
-  </si>
-  <si>
-    <t>0.7991,0.0878,0.0312,0.0136</t>
-  </si>
-  <si>
-    <t>0.9214,0.0193,0.0090,0.0058</t>
-  </si>
-  <si>
-    <t>0.8388,0.0884,0.0380,0.0046</t>
-  </si>
-  <si>
-    <t>0.9082,0.0381,0.0124,0.0051</t>
-  </si>
-  <si>
-    <t>0.9121,0.0229,0.0136,0.0086</t>
-  </si>
-  <si>
-    <t>0.8552,0.0707,0.0133,0.0053</t>
-  </si>
-  <si>
-    <t>0.6924,0.1382,0.0743,0.0205</t>
-  </si>
-  <si>
-    <t>0.8051,0.0535,0.0427,0.0233</t>
-  </si>
-  <si>
-    <t>0.9821,0.0089,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9117,0.0124,0.0751,0.0007</t>
-  </si>
-  <si>
-    <t>0.9049,0.0684,0.0365,0.0008</t>
-  </si>
-  <si>
-    <t>0.9359,0.0119,0.0549,0.0002</t>
-  </si>
-  <si>
-    <t>0.9116,0.0514,0.0358,0.0005</t>
-  </si>
-  <si>
-    <t>0.5004,0.6546,0.0414,0.0008</t>
-  </si>
-  <si>
-    <t>0.7706,0.2275,0.0480,0.0015</t>
-  </si>
-  <si>
-    <t>0.7399,0.1543,0.0464,0.0097</t>
-  </si>
-  <si>
-    <t>0.5957,0.3830,0.0665,0.0070</t>
-  </si>
-  <si>
-    <t>0.5273,0.5677,0.0836,0.0010</t>
-  </si>
-  <si>
-    <t>0.9827,0.0046,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9757,0.0056,0.0121,0.0001</t>
-  </si>
-  <si>
-    <t>0.9701,0.0039,0.0234,0.0002</t>
-  </si>
-  <si>
-    <t>0.9721,0.0047,0.0176,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0016,0.0117,0.0001</t>
-  </si>
-  <si>
-    <t>0.9053,0.0256,0.0906,0.0005</t>
-  </si>
-  <si>
-    <t>0.4510,0.0138,0.7401,0.0004</t>
-  </si>
-  <si>
-    <t>0.5974,0.4716,0.0730,0.0017</t>
-  </si>
-  <si>
-    <t>0.8452,0.1056,0.0519,0.0018</t>
-  </si>
-  <si>
-    <t>0.3845,0.0512,0.7384,0.0090</t>
-  </si>
-  <si>
-    <t>0.7288,0.1469,0.1321,0.0013</t>
-  </si>
-  <si>
-    <t>0.8678,0.1040,0.0263,0.0019</t>
-  </si>
-  <si>
-    <t>0.6843,0.1859,0.2123,0.0075</t>
-  </si>
-  <si>
-    <t>0.7970,0.0974,0.0516,0.0061</t>
-  </si>
-  <si>
-    <t>0.9429,0.0256,0.0213,0.0005</t>
-  </si>
-  <si>
-    <t>0.6175,0.1548,0.1191,0.0006</t>
-  </si>
-  <si>
-    <t>0.9648,0.0050,0.0177,0.0002</t>
-  </si>
-  <si>
-    <t>0.9916,0.0007,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9538,0.0085,0.0238,0.0003</t>
-  </si>
-  <si>
-    <t>0.9611,0.0051,0.0346,0.0001</t>
-  </si>
-  <si>
-    <t>0.4190,0.5736,0.0615,0.0007</t>
-  </si>
-  <si>
-    <t>0.8552,0.0121,0.2016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9377,0.0387,0.0076,0.0016</t>
-  </si>
-  <si>
-    <t>0.6479,0.5899,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.0702,0.9587,0.0192,0.0006</t>
-  </si>
-  <si>
-    <t>0.3043,0.8079,0.0388,0.0003</t>
-  </si>
-  <si>
-    <t>0.8358,0.0134,0.1903,0.0010</t>
-  </si>
-  <si>
-    <t>0.7444,0.0097,0.4076,0.0004</t>
-  </si>
-  <si>
-    <t>0.9709,0.0074,0.0167,0.0001</t>
-  </si>
-  <si>
-    <t>0.7153,0.0066,0.4549,0.0002</t>
-  </si>
-  <si>
-    <t>0.8611,0.0096,0.1990,0.0002</t>
-  </si>
-  <si>
-    <t>0.8705,0.0135,0.1397,0.0003</t>
-  </si>
-  <si>
-    <t>0.9015,0.0346,0.0288,0.0045</t>
-  </si>
-  <si>
-    <t>0.8906,0.0266,0.0125,0.0077</t>
-  </si>
-  <si>
-    <t>0.7940,0.1202,0.0790,0.0079</t>
-  </si>
-  <si>
-    <t>0.2287,0.2685,0.7732,0.0094</t>
-  </si>
-  <si>
-    <t>0.8272,0.0513,0.0253,0.0186</t>
-  </si>
-  <si>
-    <t>0.8399,0.0323,0.0262,0.0193</t>
-  </si>
-  <si>
-    <t>0.6989,0.1719,0.0778,0.0084</t>
-  </si>
-  <si>
-    <t>0.6554,0.0900,0.1640,0.0003</t>
-  </si>
-  <si>
-    <t>0.7855,0.0128,0.2465,0.0001</t>
-  </si>
-  <si>
-    <t>0.8815,0.0242,0.0754,0.0008</t>
-  </si>
-  <si>
-    <t>0.1420,0.4519,0.6041,0.0002</t>
-  </si>
-  <si>
-    <t>0.3145,0.0029,0.9015,0.0001</t>
-  </si>
-  <si>
-    <t>0.6498,0.5215,0.0275,0.0006</t>
-  </si>
-  <si>
-    <t>0.0236,0.9799,0.0401,0.0004</t>
-  </si>
-  <si>
-    <t>0.7593,0.1137,0.1508,0.0007</t>
-  </si>
-  <si>
-    <t>0.9641,0.0098,0.0062,0.0009</t>
-  </si>
-  <si>
-    <t>0.6116,0.1625,0.3556,0.0083</t>
-  </si>
-  <si>
-    <t>0.6155,0.2315,0.0911,0.0001</t>
-  </si>
-  <si>
-    <t>0.7677,0.1305,0.0587,0.0001</t>
-  </si>
-  <si>
-    <t>0.0500,0.9524,0.0345,0.0001</t>
-  </si>
-  <si>
-    <t>0.5377,0.3836,0.0410,0.0001</t>
-  </si>
-  <si>
-    <t>0.8597,0.0546,0.0492,0.0051</t>
-  </si>
-  <si>
-    <t>0.9056,0.0334,0.0275,0.0042</t>
-  </si>
-  <si>
-    <t>0.9639,0.0101,0.0059,0.0011</t>
-  </si>
-  <si>
-    <t>0.9421,0.0198,0.0213,0.0015</t>
-  </si>
-  <si>
-    <t>0.9513,0.0124,0.0200,0.0006</t>
-  </si>
-  <si>
-    <t>0.9718,0.0084,0.0037,0.0011</t>
-  </si>
-  <si>
-    <t>0.9019,0.0247,0.0487,0.0001</t>
-  </si>
-  <si>
-    <t>0.7734,0.0354,0.1857,0.0001</t>
-  </si>
-  <si>
-    <t>0.6992,0.0134,0.4306,0.0001</t>
-  </si>
-  <si>
-    <t>0.8590,0.0188,0.1408,0.0003</t>
-  </si>
-  <si>
-    <t>0.3629,0.2758,0.3207,0.0002</t>
-  </si>
-  <si>
-    <t>0.8615,0.1008,0.0308,0.0002</t>
-  </si>
-  <si>
-    <t>0.7116,0.1264,0.0426,0.0187</t>
-  </si>
-  <si>
-    <t>0.8455,0.0567,0.0400,0.0076</t>
-  </si>
-  <si>
-    <t>0.8767,0.0543,0.0276,0.0038</t>
-  </si>
-  <si>
-    <t>0.8953,0.0386,0.0197,0.0053</t>
-  </si>
-  <si>
-    <t>0.7191,0.1631,0.0563,0.0145</t>
-  </si>
-  <si>
-    <t>0.8094,0.0912,0.0208,0.0058</t>
-  </si>
-  <si>
-    <t>0.4908,0.3355,0.1088,0.0296</t>
-  </si>
-  <si>
-    <t>0.7982,0.0819,0.0415,0.0103</t>
-  </si>
-  <si>
-    <t>0.8603,0.0560,0.0189,0.0078</t>
-  </si>
-  <si>
-    <t>0.8443,0.0373,0.0229,0.0168</t>
-  </si>
-  <si>
-    <t>0.8458,0.0637,0.0315,0.0099</t>
-  </si>
-  <si>
-    <t>0.7499,0.0788,0.0445,0.0313</t>
-  </si>
-  <si>
-    <t>0.8642,0.0299,0.0177,0.0144</t>
-  </si>
-  <si>
-    <t>0.8826,0.0444,0.0226,0.0061</t>
-  </si>
-  <si>
-    <t>0.8832,0.0449,0.0192,0.0087</t>
-  </si>
-  <si>
-    <t>0.8518,0.0473,0.0323,0.0097</t>
-  </si>
-  <si>
-    <t>0.3794,0.0098,0.8107,0.0014</t>
-  </si>
-  <si>
-    <t>0.9048,0.0154,0.1084,0.0002</t>
-  </si>
-  <si>
-    <t>0.9848,0.0041,0.0057,0.0001</t>
-  </si>
-  <si>
-    <t>0.9219,0.0257,0.0404,0.0008</t>
-  </si>
-  <si>
-    <t>0.4819,0.5772,0.0640,0.0030</t>
-  </si>
-  <si>
-    <t>0.6412,0.3854,0.0803,0.0033</t>
-  </si>
-  <si>
-    <t>0.4686,0.5514,0.1072,0.0072</t>
-  </si>
-  <si>
-    <t>0.5592,0.3304,0.1555,0.0078</t>
-  </si>
-  <si>
-    <t>0.2792,0.7625,0.1130,0.0017</t>
-  </si>
-  <si>
-    <t>0.0820,0.9282,0.0541,0.0036</t>
-  </si>
-  <si>
-    <t>0.7782,0.1769,0.0579,0.0028</t>
-  </si>
-  <si>
-    <t>0.9423,0.0236,0.0125,0.0011</t>
-  </si>
-  <si>
-    <t>0.9290,0.0205,0.0459,0.0005</t>
-  </si>
-  <si>
-    <t>0.9606,0.0108,0.0188,0.0002</t>
-  </si>
-  <si>
-    <t>0.9251,0.0463,0.0306,0.0003</t>
-  </si>
-  <si>
-    <t>0.8850,0.0608,0.0432,0.0011</t>
-  </si>
-  <si>
-    <t>0.2251,0.8876,0.0275,0.0005</t>
-  </si>
-  <si>
-    <t>0.5927,0.5472,0.0480,0.0010</t>
-  </si>
-  <si>
-    <t>0.9521,0.0387,0.0127,0.0002</t>
-  </si>
-  <si>
-    <t>0.1992,0.7973,0.1987,0.0017</t>
-  </si>
-  <si>
-    <t>0.6791,0.3112,0.0938,0.0016</t>
-  </si>
-  <si>
-    <t>0.8767,0.0432,0.0353,0.0056</t>
-  </si>
-  <si>
-    <t>0.7229,0.1483,0.0626,0.0141</t>
-  </si>
-  <si>
-    <t>0.9102,0.0212,0.0195,0.0069</t>
-  </si>
-  <si>
-    <t>0.8784,0.0327,0.0288,0.0083</t>
-  </si>
-  <si>
-    <t>0.8109,0.0577,0.0779,0.0113</t>
-  </si>
-  <si>
-    <t>0.8618,0.0582,0.0461,0.0050</t>
-  </si>
-  <si>
-    <t>0.8615,0.0845,0.0459,0.0049</t>
-  </si>
-  <si>
-    <t>0.8699,0.0684,0.0295,0.0053</t>
-  </si>
-  <si>
-    <t>0.8318,0.0635,0.0365,0.0111</t>
-  </si>
-  <si>
-    <t>0.7617,0.0528,0.0384,0.0237</t>
-  </si>
-  <si>
-    <t>0.8163,0.1477,0.0310,0.0001</t>
-  </si>
-  <si>
-    <t>0.9542,0.0053,0.0368,0.0000</t>
-  </si>
-  <si>
-    <t>0.8596,0.0201,0.1282,0.0001</t>
-  </si>
-  <si>
-    <t>0.9587,0.0042,0.0367,0.0001</t>
-  </si>
-  <si>
-    <t>0.9847,0.0056,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9431,0.0242,0.0210,0.0006</t>
-  </si>
-  <si>
-    <t>0.9683,0.0100,0.0149,0.0003</t>
-  </si>
-  <si>
-    <t>0.9707,0.0118,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.9759,0.0084,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9594,0.0065,0.0103,0.0017</t>
-  </si>
-  <si>
-    <t>0.8748,0.0456,0.0470,0.0044</t>
-  </si>
-  <si>
-    <t>0.8702,0.0251,0.0144,0.0134</t>
-  </si>
-  <si>
-    <t>0.2644,0.2411,0.5915,0.0021</t>
-  </si>
-  <si>
-    <t>0.9140,0.0230,0.0144,0.0049</t>
-  </si>
-  <si>
-    <t>0.7553,0.2185,0.0571,0.0023</t>
-  </si>
-  <si>
-    <t>0.8090,0.1136,0.0672,0.0073</t>
-  </si>
-  <si>
-    <t>0.8370,0.0508,0.0553,0.0088</t>
-  </si>
-  <si>
-    <t>0.9253,0.0224,0.0239,0.0027</t>
-  </si>
-  <si>
-    <t>0.9158,0.0484,0.0201,0.0016</t>
-  </si>
-  <si>
-    <t>0.7908,0.0793,0.0370,0.0158</t>
-  </si>
-  <si>
-    <t>0.1069,0.3364,0.8574,0.0162</t>
-  </si>
-  <si>
-    <t>0.7212,0.1195,0.0333,0.0209</t>
-  </si>
-  <si>
-    <t>0.5701,0.1330,0.0437,0.0559</t>
-  </si>
-  <si>
-    <t>0.6743,0.3123,0.0768,0.0041</t>
-  </si>
-  <si>
-    <t>0.9198,0.0474,0.0141,0.0012</t>
-  </si>
-  <si>
-    <t>0.9227,0.0277,0.0119,0.0036</t>
-  </si>
-  <si>
-    <t>0.8262,0.0533,0.0491,0.0130</t>
-  </si>
-  <si>
-    <t>0.9125,0.0742,0.0216,0.0007</t>
-  </si>
-  <si>
-    <t>0.9050,0.0782,0.0292,0.0003</t>
-  </si>
-  <si>
-    <t>0.6885,0.2192,0.0778,0.0103</t>
-  </si>
-  <si>
-    <t>0.8577,0.0693,0.0202,0.0059</t>
-  </si>
-  <si>
-    <t>0.8275,0.0652,0.0299,0.0116</t>
-  </si>
-  <si>
-    <t>0.8553,0.0307,0.0161,0.0197</t>
-  </si>
-  <si>
-    <t>0.8636,0.0692,0.0460,0.0046</t>
-  </si>
-  <si>
-    <t>0.8764,0.0217,0.0185,0.0154</t>
-  </si>
-  <si>
-    <t>0.8550,0.0648,0.0221,0.0070</t>
-  </si>
-  <si>
-    <t>0.7239,0.2083,0.0572,0.0082</t>
-  </si>
-  <si>
-    <t>0.8081,0.1444,0.0526,0.0026</t>
-  </si>
-  <si>
-    <t>0.7848,0.1702,0.0435,0.0042</t>
-  </si>
-  <si>
-    <t>0.8127,0.1797,0.0428,0.0029</t>
-  </si>
-  <si>
-    <t>0.8430,0.0686,0.0341,0.0061</t>
-  </si>
-  <si>
-    <t>0.8631,0.0512,0.0263,0.0063</t>
-  </si>
-  <si>
-    <t>0.7898,0.0977,0.0409,0.0081</t>
-  </si>
-  <si>
-    <t>0.8583,0.0597,0.0491,0.0047</t>
-  </si>
-  <si>
-    <t>0.9055,0.0372,0.0277,0.0032</t>
-  </si>
-  <si>
-    <t>0.0745,0.2344,0.9136,0.0010</t>
-  </si>
-  <si>
-    <t>0.6886,0.1403,0.0952,0.0123</t>
-  </si>
-  <si>
-    <t>0.8629,0.0075,0.1359,0.0002</t>
-  </si>
-  <si>
-    <t>0.9594,0.0144,0.0255,0.0001</t>
-  </si>
-  <si>
-    <t>0.9363,0.0062,0.0676,0.0001</t>
-  </si>
-  <si>
-    <t>0.6109,0.0242,0.4121,0.0004</t>
-  </si>
-  <si>
-    <t>0.9838,0.0011,0.0135,0.0000</t>
-  </si>
-  <si>
-    <t>0.9448,0.0031,0.0615,0.0001</t>
-  </si>
-  <si>
-    <t>0.8822,0.0064,0.1704,0.0003</t>
-  </si>
-  <si>
-    <t>0.8722,0.0173,0.1481,0.0008</t>
-  </si>
-  <si>
-    <t>0.8478,0.0676,0.0937,0.0024</t>
-  </si>
-  <si>
-    <t>0.9411,0.0224,0.0331,0.0002</t>
-  </si>
-  <si>
-    <t>0.9069,0.0181,0.0977,0.0002</t>
-  </si>
-  <si>
-    <t>0.9112,0.0604,0.0374,0.0007</t>
-  </si>
-  <si>
-    <t>0.9358,0.0553,0.0177,0.0002</t>
-  </si>
-  <si>
-    <t>0.8980,0.0365,0.0610,0.0014</t>
-  </si>
-  <si>
-    <t>0.9282,0.0317,0.0340,0.0004</t>
-  </si>
-  <si>
-    <t>0.7263,0.2728,0.0556,0.0036</t>
-  </si>
-  <si>
-    <t>0.7432,0.2086,0.0655,0.0043</t>
-  </si>
-  <si>
-    <t>0.5827,0.4260,0.0988,0.0062</t>
-  </si>
-  <si>
-    <t>0.9000,0.0265,0.0172,0.0093</t>
-  </si>
-  <si>
-    <t>0.7940,0.0694,0.0474,0.0120</t>
-  </si>
-  <si>
-    <t>0.9250,0.0281,0.0366,0.0008</t>
-  </si>
-  <si>
-    <t>0.9222,0.0471,0.0266,0.0006</t>
-  </si>
-  <si>
-    <t>0.8965,0.0372,0.0596,0.0011</t>
-  </si>
-  <si>
-    <t>0.9603,0.0053,0.0277,0.0002</t>
-  </si>
-  <si>
-    <t>0.9390,0.0220,0.0144,0.0015</t>
-  </si>
-  <si>
-    <t>0.7682,0.0537,0.2336,0.0023</t>
-  </si>
-  <si>
-    <t>0.9108,0.0065,0.1128,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0012,0.0121,0.0001</t>
-  </si>
-  <si>
-    <t>0.9716,0.0014,0.0229,0.0000</t>
-  </si>
-  <si>
-    <t>0.9503,0.0108,0.0192,0.0003</t>
-  </si>
-  <si>
-    <t>0.9017,0.0226,0.0091,0.0101</t>
-  </si>
-  <si>
-    <t>0.7439,0.1738,0.0595,0.0082</t>
-  </si>
-  <si>
-    <t>0.8274,0.0867,0.0293,0.0066</t>
-  </si>
-  <si>
-    <t>0.8856,0.0234,0.0212,0.0117</t>
-  </si>
-  <si>
-    <t>0.8494,0.0503,0.0205,0.0074</t>
-  </si>
-  <si>
-    <t>0.7995,0.0861,0.0446,0.0100</t>
-  </si>
-  <si>
-    <t>0.8464,0.0516,0.0167,0.0106</t>
-  </si>
-  <si>
-    <t>0.8836,0.0213,0.0135,0.0134</t>
-  </si>
-  <si>
-    <t>0.9166,0.0251,0.0385,0.0014</t>
-  </si>
-  <si>
-    <t>0.8394,0.1449,0.0513,0.0006</t>
-  </si>
-  <si>
-    <t>0.8332,0.0780,0.0827,0.0043</t>
-  </si>
-  <si>
-    <t>0.7218,0.0224,0.2567,0.0004</t>
-  </si>
-  <si>
-    <t>0.7948,0.0510,0.1163,0.0024</t>
-  </si>
-  <si>
-    <t>0.8703,0.0171,0.1244,0.0004</t>
-  </si>
-  <si>
-    <t>0.2241,0.0215,0.8943,0.0005</t>
-  </si>
-  <si>
-    <t>0.9706,0.0083,0.0114,0.0001</t>
-  </si>
-  <si>
-    <t>0.5520,0.0054,0.6996,0.0004</t>
-  </si>
-  <si>
-    <t>0.9578,0.0039,0.0468,0.0001</t>
-  </si>
-  <si>
-    <t>0.9341,0.0205,0.0390,0.0004</t>
-  </si>
-  <si>
-    <t>0.9389,0.0101,0.0425,0.0005</t>
-  </si>
-  <si>
-    <t>0.9669,0.0065,0.0150,0.0004</t>
-  </si>
-  <si>
-    <t>0.9773,0.0071,0.0072,0.0001</t>
-  </si>
-  <si>
-    <t>0.7904,0.1101,0.0473,0.0081</t>
-  </si>
-  <si>
-    <t>0.6283,0.3324,0.0321,0.0052</t>
-  </si>
-  <si>
-    <t>0.8396,0.0757,0.0386,0.0082</t>
-  </si>
-  <si>
-    <t>0.9027,0.0188,0.0259,0.0089</t>
-  </si>
-  <si>
-    <t>0.6982,0.0756,0.0638,0.0342</t>
-  </si>
-  <si>
-    <t>0.7491,0.1142,0.0418,0.0130</t>
-  </si>
-  <si>
-    <t>0.8159,0.0545,0.0411,0.0153</t>
-  </si>
-  <si>
-    <t>0.7716,0.0729,0.0265,0.0228</t>
-  </si>
-  <si>
-    <t>0.9716,0.0140,0.0097,0.0001</t>
-  </si>
-  <si>
-    <t>0.9283,0.0101,0.0692,0.0001</t>
-  </si>
-  <si>
-    <t>0.9315,0.0027,0.0629,0.0001</t>
-  </si>
-  <si>
-    <t>0.9505,0.0102,0.0304,0.0002</t>
-  </si>
-  <si>
-    <t>0.9641,0.0033,0.0259,0.0003</t>
-  </si>
-  <si>
-    <t>0.9654,0.0089,0.0126,0.0004</t>
-  </si>
-  <si>
-    <t>0.9722,0.0064,0.0142,0.0000</t>
-  </si>
-  <si>
-    <t>0.9690,0.0024,0.0208,0.0004</t>
-  </si>
-  <si>
-    <t>0.8631,0.0711,0.0247,0.0045</t>
-  </si>
-  <si>
-    <t>0.9522,0.0108,0.0253,0.0010</t>
-  </si>
-  <si>
-    <t>0.9584,0.0138,0.0099,0.0013</t>
-  </si>
-  <si>
-    <t>0.9192,0.0107,0.0216,0.0041</t>
-  </si>
-  <si>
-    <t>0.9305,0.0122,0.0093,0.0076</t>
-  </si>
-  <si>
-    <t>0.9163,0.0317,0.0297,0.0020</t>
+    <t>0.9053,0.0067,0.0250,0.0341</t>
+  </si>
+  <si>
+    <t>0.0056,0.0002,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.9424,0.0013,0.0004,0.0593</t>
+  </si>
+  <si>
+    <t>0.4308,0.0022,0.0629,0.4408</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0016,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0053,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.7572,0.0300,0.2280,0.0032</t>
+  </si>
+  <si>
+    <t>0.2418,0.0123,0.8559,0.0015</t>
+  </si>
+  <si>
+    <t>0.8648,0.0334,0.0819,0.0013</t>
+  </si>
+  <si>
+    <t>0.0192,0.0104,0.9735,0.0031</t>
+  </si>
+  <si>
+    <t>0.8689,0.0611,0.0789,0.0053</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.9938,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.0319,0.9651,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0082,0.9871,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.9979,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.8207,0.0032,0.0348,0.0814</t>
+  </si>
+  <si>
+    <t>0.8992,0.0073,0.0689,0.0091</t>
+  </si>
+  <si>
+    <t>0.0061,0.0007,0.9951,0.0016</t>
+  </si>
+  <si>
+    <t>0.0598,0.0029,0.9644,0.0034</t>
+  </si>
+  <si>
+    <t>0.1315,0.0029,0.9379,0.0008</t>
+  </si>
+  <si>
+    <t>0.0112,0.0014,0.9682,0.0496</t>
+  </si>
+  <si>
+    <t>0.0095,0.0134,0.9723,0.0221</t>
+  </si>
+  <si>
+    <t>0.6930,0.4980,0.0043,0.0021</t>
+  </si>
+  <si>
+    <t>0.7002,0.0219,0.4077,0.0031</t>
+  </si>
+  <si>
+    <t>0.0039,0.0079,0.9900,0.0128</t>
+  </si>
+  <si>
+    <t>0.0057,0.9847,0.0299,0.0007</t>
+  </si>
+  <si>
+    <t>0.5048,0.0341,0.0790,0.4737</t>
+  </si>
+  <si>
+    <t>0.7733,0.1287,0.0912,0.0440</t>
+  </si>
+  <si>
+    <t>0.9362,0.0809,0.0055,0.0015</t>
+  </si>
+  <si>
+    <t>0.0553,0.9286,0.2511,0.0039</t>
+  </si>
+  <si>
+    <t>0.1116,0.5392,0.1525,0.3064</t>
+  </si>
+  <si>
+    <t>0.0840,0.0022,0.8912,0.0142</t>
+  </si>
+  <si>
+    <t>0.0828,0.0143,0.9155,0.0235</t>
+  </si>
+  <si>
+    <t>0.0594,0.0036,0.9294,0.0325</t>
+  </si>
+  <si>
+    <t>0.0513,0.0299,0.9634,0.0036</t>
+  </si>
+  <si>
+    <t>0.0133,0.9738,0.0130,0.0031</t>
+  </si>
+  <si>
+    <t>0.0137,0.0175,0.9740,0.0069</t>
+  </si>
+  <si>
+    <t>0.2006,0.2523,0.0076,0.6483</t>
+  </si>
+  <si>
+    <t>0.0210,0.9499,0.0292,0.0250</t>
+  </si>
+  <si>
+    <t>0.0006,0.9969,0.0042,0.0013</t>
+  </si>
+  <si>
+    <t>0.0010,0.9932,0.0110,0.0033</t>
+  </si>
+  <si>
+    <t>0.0028,0.0428,0.9833,0.0039</t>
+  </si>
+  <si>
+    <t>0.0104,0.0510,0.9769,0.0106</t>
+  </si>
+  <si>
+    <t>0.0730,0.0064,0.9421,0.0107</t>
+  </si>
+  <si>
+    <t>0.0271,0.0020,0.9844,0.0025</t>
+  </si>
+  <si>
+    <t>0.0029,0.0195,0.9830,0.0144</t>
+  </si>
+  <si>
+    <t>0.0608,0.0725,0.9277,0.0064</t>
+  </si>
+  <si>
+    <t>0.9634,0.0590,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9917,0.0021,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.9387,0.0403,0.0055,0.0118</t>
+  </si>
+  <si>
+    <t>0.0395,0.1981,0.9410,0.0321</t>
+  </si>
+  <si>
+    <t>0.9975,0.0011,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0038,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0013,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.8925,0.9430,0.0011</t>
+  </si>
+  <si>
+    <t>0.0059,0.0489,0.9863,0.0036</t>
+  </si>
+  <si>
+    <t>0.0455,0.1386,0.9096,0.0232</t>
+  </si>
+  <si>
+    <t>0.0003,0.9736,0.9749,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0073,0.9922,0.0048</t>
+  </si>
+  <si>
+    <t>0.0466,0.9479,0.0103,0.0041</t>
+  </si>
+  <si>
+    <t>0.2854,0.8217,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.5973,0.0582,0.5075,0.0263</t>
+  </si>
+  <si>
+    <t>0.2681,0.1480,0.7947,0.0067</t>
+  </si>
+  <si>
+    <t>0.0183,0.0103,0.9854,0.0053</t>
+  </si>
+  <si>
+    <t>0.0016,0.9715,0.7496,0.0003</t>
+  </si>
+  <si>
+    <t>0.0400,0.3827,0.8529,0.0012</t>
+  </si>
+  <si>
+    <t>0.0071,0.9766,0.0882,0.0011</t>
+  </si>
+  <si>
+    <t>0.0048,0.9659,0.4723,0.0025</t>
+  </si>
+  <si>
+    <t>0.0865,0.0033,0.0076,0.9441</t>
+  </si>
+  <si>
+    <t>0.0016,0.0018,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0194,0.0001,0.0001,0.9962</t>
+  </si>
+  <si>
+    <t>0.0275,0.0015,0.0067,0.9828</t>
+  </si>
+  <si>
+    <t>0.0004,0.0020,0.0005,0.9994</t>
+  </si>
+  <si>
+    <t>0.0087,0.0028,0.0011,0.9949</t>
+  </si>
+  <si>
+    <t>0.0043,0.9667,0.7350,0.0010</t>
+  </si>
+  <si>
+    <t>0.0124,0.3755,0.9332,0.0016</t>
+  </si>
+  <si>
+    <t>0.0142,0.0997,0.9474,0.0061</t>
+  </si>
+  <si>
+    <t>0.0183,0.4120,0.8866,0.0024</t>
+  </si>
+  <si>
+    <t>0.0001,0.9960,0.8279,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.9579,0.2085,0.0008</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9897,0.0097,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0067,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0042,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0045,0.0013,0.9923,0.0053</t>
+  </si>
+  <si>
+    <t>0.0422,0.0057,0.9779,0.0035</t>
+  </si>
+  <si>
+    <t>0.9598,0.0029,0.0056,0.0186</t>
+  </si>
+  <si>
+    <t>0.1178,0.0052,0.9324,0.0041</t>
+  </si>
+  <si>
+    <t>0.0103,0.9828,0.0016,0.0020</t>
+  </si>
+  <si>
+    <t>0.0074,0.9866,0.0035,0.0029</t>
+  </si>
+  <si>
+    <t>0.0102,0.9818,0.0017,0.0039</t>
+  </si>
+  <si>
+    <t>0.0033,0.9901,0.0029,0.0038</t>
+  </si>
+  <si>
+    <t>0.0012,0.9963,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.0035,0.9904,0.0011,0.0030</t>
+  </si>
+  <si>
+    <t>0.9638,0.0632,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.8913,0.0064,0.1021,0.0045</t>
+  </si>
+  <si>
+    <t>0.4216,0.0032,0.7484,0.0007</t>
+  </si>
+  <si>
+    <t>0.3241,0.0495,0.5870,0.1052</t>
+  </si>
+  <si>
+    <t>0.3971,0.0453,0.6738,0.0154</t>
+  </si>
+  <si>
+    <t>0.0386,0.1010,0.0330,0.9206</t>
+  </si>
+  <si>
+    <t>0.0025,0.9927,0.0181,0.0011</t>
+  </si>
+  <si>
+    <t>0.0059,0.9863,0.0089,0.0035</t>
+  </si>
+  <si>
+    <t>0.0002,0.9965,0.0014,0.0189</t>
+  </si>
+  <si>
+    <t>0.0028,0.9704,0.5797,0.0018</t>
+  </si>
+  <si>
+    <t>0.0310,0.9679,0.0244,0.0003</t>
+  </si>
+  <si>
+    <t>0.7380,0.3792,0.0147,0.0022</t>
+  </si>
+  <si>
+    <t>0.9400,0.0667,0.0065,0.0041</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9891,0.0086,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.5370,0.9551,0.0009</t>
+  </si>
+  <si>
+    <t>0.0185,0.8121,0.7002,0.0032</t>
+  </si>
+  <si>
+    <t>0.0162,0.0209,0.9862,0.0006</t>
+  </si>
+  <si>
+    <t>0.0365,0.0397,0.9452,0.0063</t>
+  </si>
+  <si>
+    <t>0.9870,0.0009,0.0079,0.0002</t>
+  </si>
+  <si>
+    <t>0.8945,0.0300,0.0513,0.0041</t>
+  </si>
+  <si>
+    <t>0.0452,0.0014,0.9881,0.0010</t>
+  </si>
+  <si>
+    <t>0.5833,0.0407,0.5370,0.0083</t>
+  </si>
+  <si>
+    <t>0.2609,0.0019,0.0043,0.8678</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0078,0.0029,0.0009,0.9960</t>
+  </si>
+  <si>
+    <t>0.0100,0.0005,0.0048,0.9929</t>
+  </si>
+  <si>
+    <t>0.0023,0.5150,0.9386,0.0037</t>
+  </si>
+  <si>
+    <t>0.9947,0.0011,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.0616,0.9295,0.0072,0.0181</t>
+  </si>
+  <si>
+    <t>0.9902,0.0023,0.0011,0.0033</t>
+  </si>
+  <si>
+    <t>0.7497,0.3877,0.0051,0.0018</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.7628,0.0025,0.0078,0.3030</t>
+  </si>
+  <si>
+    <t>0.9869,0.0019,0.0012,0.0052</t>
+  </si>
+  <si>
+    <t>0.0088,0.2302,0.8826,0.0906</t>
+  </si>
+  <si>
+    <t>0.9829,0.0004,0.0011,0.0102</t>
+  </si>
+  <si>
+    <t>0.9374,0.0012,0.0006,0.0626</t>
+  </si>
+  <si>
+    <t>0.2723,0.6725,0.0050,0.0197</t>
+  </si>
+  <si>
+    <t>0.9491,0.0431,0.0045,0.0037</t>
+  </si>
+  <si>
+    <t>0.9732,0.0136,0.0102,0.0014</t>
+  </si>
+  <si>
+    <t>0.0762,0.8743,0.0536,0.0144</t>
+  </si>
+  <si>
+    <t>0.9631,0.0232,0.0090,0.0014</t>
+  </si>
+  <si>
+    <t>0.9920,0.0041,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0003,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9956,0.0002,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.8992,0.1472,0.0037,0.0021</t>
+  </si>
+  <si>
+    <t>0.9079,0.1204,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.7536,0.3779,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.2003,0.0628,0.8978,0.0051</t>
+  </si>
+  <si>
+    <t>0.9962,0.0030,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9710,0.0147,0.0040,0.0044</t>
+  </si>
+  <si>
+    <t>0.9941,0.0016,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9656,0.0220,0.0030,0.0062</t>
+  </si>
+  <si>
+    <t>0.0034,0.0028,0.9979,0.0005</t>
+  </si>
+  <si>
+    <t>0.9744,0.0260,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.0073,0.0027,0.9860,0.0093</t>
+  </si>
+  <si>
+    <t>0.0175,0.0434,0.9650,0.0083</t>
+  </si>
+  <si>
+    <t>0.0295,0.0033,0.9801,0.0050</t>
+  </si>
+  <si>
+    <t>0.0022,0.0371,0.9926,0.0020</t>
+  </si>
+  <si>
+    <t>0.0230,0.0055,0.9853,0.0021</t>
+  </si>
+  <si>
+    <t>0.0200,0.0042,0.9859,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0016,0.9971,0.0031</t>
+  </si>
+  <si>
+    <t>0.3054,0.0252,0.7920,0.0114</t>
+  </si>
+  <si>
+    <t>0.0314,0.0316,0.9661,0.0027</t>
+  </si>
+  <si>
+    <t>0.4096,0.0116,0.7213,0.0039</t>
+  </si>
+  <si>
+    <t>0.2327,0.1236,0.6068,0.0089</t>
+  </si>
+  <si>
+    <t>0.1005,0.1199,0.8939,0.0056</t>
+  </si>
+  <si>
+    <t>0.5559,0.1405,0.2416,0.0089</t>
+  </si>
+  <si>
+    <t>0.3248,0.5139,0.3309,0.1030</t>
+  </si>
+  <si>
+    <t>0.3088,0.4539,0.3439,0.0535</t>
+  </si>
+  <si>
+    <t>0.1613,0.8918,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.0498,0.9645,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.8273,0.2899,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9829,0.0188,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9385,0.1116,0.0034,0.0014</t>
+  </si>
+  <si>
+    <t>0.9777,0.0058,0.0084,0.0017</t>
+  </si>
+  <si>
+    <t>0.9291,0.0078,0.0384,0.0089</t>
+  </si>
+  <si>
+    <t>0.7459,0.0089,0.0320,0.1691</t>
+  </si>
+  <si>
+    <t>0.9683,0.0043,0.0195,0.0004</t>
+  </si>
+  <si>
+    <t>0.8692,0.0090,0.1044,0.0106</t>
+  </si>
+  <si>
+    <t>0.0333,0.0174,0.9338,0.0478</t>
+  </si>
+  <si>
+    <t>0.0786,0.2160,0.8265,0.0110</t>
+  </si>
+  <si>
+    <t>0.2179,0.0059,0.8773,0.0056</t>
+  </si>
+  <si>
+    <t>0.3706,0.0090,0.6680,0.0124</t>
+  </si>
+  <si>
+    <t>0.0447,0.7826,0.5131,0.0093</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9902,0.0061,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9929,0.0035,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9858,0.0090,0.0017,0.0027</t>
+  </si>
+  <si>
+    <t>0.9949,0.0029,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0236,0.0144,0.9887,0.0015</t>
+  </si>
+  <si>
+    <t>0.1693,0.2997,0.6712,0.0443</t>
+  </si>
+  <si>
+    <t>0.9259,0.0217,0.0393,0.0041</t>
+  </si>
+  <si>
+    <t>0.0563,0.0017,0.9784,0.0009</t>
+  </si>
+  <si>
+    <t>0.0161,0.0199,0.9650,0.0139</t>
+  </si>
+  <si>
+    <t>0.0334,0.2310,0.8797,0.0039</t>
+  </si>
+  <si>
+    <t>0.0764,0.0030,0.9665,0.0006</t>
+  </si>
+  <si>
+    <t>0.0288,0.0026,0.9837,0.0016</t>
+  </si>
+  <si>
+    <t>0.0027,0.0103,0.9950,0.0014</t>
+  </si>
+  <si>
+    <t>0.0052,0.0025,0.9881,0.0112</t>
+  </si>
+  <si>
+    <t>0.0657,0.0261,0.9122,0.0095</t>
+  </si>
+  <si>
+    <t>0.7453,0.0010,0.2354,0.0109</t>
+  </si>
+  <si>
+    <t>0.9415,0.0035,0.0605,0.0014</t>
+  </si>
+  <si>
+    <t>0.9740,0.0146,0.0042,0.0034</t>
+  </si>
+  <si>
+    <t>0.9951,0.0036,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0024,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0019,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0077,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0497,0.3359,0.6629,0.0230</t>
+  </si>
+  <si>
+    <t>0.0322,0.1842,0.9402,0.0066</t>
+  </si>
+  <si>
+    <t>0.0141,0.0125,0.9734,0.0181</t>
+  </si>
+  <si>
+    <t>0.0134,0.0048,0.9750,0.0068</t>
+  </si>
+  <si>
+    <t>0.0125,0.0034,0.9918,0.0007</t>
+  </si>
+  <si>
+    <t>0.7109,0.0137,0.1784,0.0814</t>
+  </si>
+  <si>
+    <t>0.2412,0.0019,0.8950,0.0017</t>
+  </si>
+  <si>
+    <t>0.2667,0.0266,0.6980,0.0630</t>
+  </si>
+  <si>
+    <t>0.7842,0.0016,0.0072,0.2393</t>
+  </si>
+  <si>
+    <t>0.0131,0.0113,0.0020,0.9908</t>
+  </si>
+  <si>
+    <t>0.0550,0.0003,0.0013,0.9811</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.0026,0.9982</t>
+  </si>
+  <si>
+    <t>0.0029,0.0006,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.0840,0.0040,0.0040,0.9621</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1961,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -2135,7 +2129,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2157,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2205,7 +2199,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2213,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2227,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2283,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2311,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2325,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2401,7 +2395,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2451,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2465,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2479,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2493,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2507,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2521,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2549,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2563,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2625,7 +2619,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2633,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2647,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2661,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2675,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2689,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2807,7 +2801,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2815,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2829,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2843,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2905,7 +2899,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2919,7 +2913,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2927,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2941,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2955,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2983,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +2997,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3011,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3025,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3039,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3053,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3067,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3081,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3095,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3109,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3123,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3137,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3151,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3403,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3431,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3459,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3487,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3557,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3571,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3591,7 +3585,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3599,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3647,7 +3641,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3655,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3669,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3818,7 +3812,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3823,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3837,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3851,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3865,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3882,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3896,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3907,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3921,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3935,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3949,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3963,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3977,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +3991,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4019,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4036,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4050,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4064,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4078,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4092,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4106,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4120,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4145,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4162,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4176,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4187,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4204,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4218,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4232,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4246,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4260,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4274,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4288,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4302,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4316,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4330,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4344,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4358,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4372,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4383,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4400,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4414,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4428,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4442,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4470,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4481,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4495,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4509,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4523,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4537,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4551,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4565,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4579,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4593,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4607,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4621,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4635,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4652,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4663,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4680,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4691,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4705,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4722,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4736,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4750,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4764,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4778,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4792,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4806,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4820,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4831,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4845,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4859,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4873,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4887,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4904,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4918,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4932,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4946,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4960,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4974,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4988,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5002,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5013,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5027,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5044,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5055,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5069,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5083,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5100,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5111,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5128,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5139,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5153,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5184,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5212,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5226,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5240,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5254,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5268,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5282,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5296,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5310,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5321,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5335,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5349,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5363,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5377,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5394,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5405,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5419,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5436,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5447,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5461,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5475,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5489,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5503,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
